--- a/siebel-crm-automation/test_data/input_data.xlsx
+++ b/siebel-crm-automation/test_data/input_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\test\test_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\siebel-crm-automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105B4AAD-4AFB-496D-84CC-2DD84113A807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C06F81-91C1-4163-B586-EA4D020F8314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
